--- a/artfynd/A 39627-2023 artfynd.xlsx
+++ b/artfynd/A 39627-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 39627-2023 artfynd.xlsx
+++ b/artfynd/A 39627-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>94189913</v>
+        <v>94189904</v>
       </c>
       <c r="B2" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>413176.5596804536</v>
+        <v>413173</v>
       </c>
       <c r="R2" t="n">
-        <v>6656218.898979314</v>
+        <v>6656330</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2021-06-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-06-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>94189914</v>
+        <v>112083118</v>
       </c>
       <c r="B3" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Öst om Sörskog Skallberget NR, Vrm</t>
+          <t>Sörskog Skallberget, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>413237.0880116016</v>
+        <v>412576</v>
       </c>
       <c r="R3" t="n">
-        <v>6656386.431919145</v>
+        <v>6656303</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>94189904</v>
+        <v>112083128</v>
       </c>
       <c r="B4" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,34 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Öst om Sörskog Skallberget NR, Vrm</t>
+          <t>Sörskog Skallberget, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>413173.1565896106</v>
+        <v>413190</v>
       </c>
       <c r="R4" t="n">
-        <v>6656329.453270309</v>
+        <v>6656475</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>94189896</v>
+        <v>112083112</v>
       </c>
       <c r="B5" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,34 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Öst om Sörskog Skallberget NR, Vrm</t>
+          <t>Sörskog Skallberget, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>413161.5639446184</v>
+        <v>412284</v>
       </c>
       <c r="R5" t="n">
-        <v>6656283.737702749</v>
+        <v>6656072</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,22 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,67 +1063,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>94190080</v>
+        <v>112083111</v>
       </c>
       <c r="B6" t="n">
-        <v>8624</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100798</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Smal trollknäppare</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Danosoma conspersum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyllenhal, 1808)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Öst om Sörskog Skallbergets NR, Vrm</t>
+          <t>Sörskog Skallberget, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>413176.5596804536</v>
+        <v>412204</v>
       </c>
       <c r="R6" t="n">
-        <v>6656218.898979314</v>
+        <v>6655989</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,27 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Satt på mossa ovanpå en silverstubbe bl a bevuxen med vedskivlav</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,14 +1142,8 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1263,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112083110</v>
+        <v>112083125</v>
       </c>
       <c r="B7" t="n">
-        <v>78277</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1303,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>412206</v>
+        <v>413016</v>
       </c>
       <c r="R7" t="n">
-        <v>6656051</v>
+        <v>6656415</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1365,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112083118</v>
+        <v>94189914</v>
       </c>
       <c r="B8" t="n">
-        <v>94336</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1381,34 +1268,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sörskog Skallberget, Vrm</t>
+          <t>Öst om Sörskog Skallberget NR, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>412577</v>
+        <v>413237</v>
       </c>
       <c r="R8" t="n">
-        <v>6656304</v>
+        <v>6656386</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1435,12 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,37 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112083125</v>
+        <v>112083127</v>
       </c>
       <c r="B9" t="n">
-        <v>89552</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79413</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>6450</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1507,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>413016</v>
+        <v>413052</v>
       </c>
       <c r="R9" t="n">
-        <v>6656415</v>
+        <v>6656343</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1569,50 +1451,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112083126</v>
+        <v>94189896</v>
       </c>
       <c r="B10" t="n">
-        <v>78706</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229497</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sörskog Skallberget, Vrm</t>
+          <t>Öst om Sörskog Skallberget NR, Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>413017</v>
+        <v>413162</v>
       </c>
       <c r="R10" t="n">
-        <v>6656342</v>
+        <v>6656283</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1639,12 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1671,50 +1548,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112083111</v>
+        <v>94189913</v>
       </c>
       <c r="B11" t="n">
-        <v>90849</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sörskog Skallberget, Vrm</t>
+          <t>Öst om Sörskog Skallberget NR, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>412205</v>
+        <v>413176</v>
       </c>
       <c r="R11" t="n">
-        <v>6655989</v>
+        <v>6656219</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1741,12 +1613,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1773,15 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112083128</v>
+        <v>112083110</v>
       </c>
       <c r="B12" t="n">
-        <v>77356</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1789,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1813,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>413190</v>
+        <v>412206</v>
       </c>
       <c r="R12" t="n">
-        <v>6656475</v>
+        <v>6656051</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1875,15 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112083112</v>
+        <v>94189906</v>
       </c>
       <c r="B13" t="n">
-        <v>79615</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1891,34 +1753,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1049</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sörskog Skallberget, Vrm</t>
+          <t>Öst om Sörskog Skallberget NR, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>412284</v>
+        <v>412178</v>
       </c>
       <c r="R13" t="n">
-        <v>6656072</v>
+        <v>6656143</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1945,12 +1807,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1977,37 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112083127</v>
+        <v>112083109</v>
       </c>
       <c r="B14" t="n">
-        <v>77773</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6450</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2017,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>413052</v>
+        <v>412192</v>
       </c>
       <c r="R14" t="n">
-        <v>6656343</v>
+        <v>6656134</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2076,6 +1933,519 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>94189905</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Öst om Sörskog Skallberget NR, Vrm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>412178</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6656143</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ekshärad</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2021-06-09</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2021-06-09</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>112083107</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Sörskog Skallberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>412192</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6656134</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ekshärad</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>94190080</v>
+      </c>
+      <c r="B17" t="n">
+        <v>8728</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100798</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Smal trollknäppare</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Danosoma conspersum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Gyllenhal, 1808)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Öst om Sörskog Skallbergets NR, Vrm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>413176</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6656219</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ekshärad</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2021-06-09</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2021-06-09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Satt på mossa ovanpå en silverstubbe bl a bevuxen med vedskivlav</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>112083108</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Sörskog Skallberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>412192</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6656134</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ekshärad</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>112083126</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Sörskog Skallberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>413017</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6656342</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ekshärad</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39627-2023 artfynd.xlsx
+++ b/artfynd/A 39627-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94189904</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112083118</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112083128</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112083112</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112083111</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112083125</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94189914</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112083127</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94189896</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94189913</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112083110</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94189906</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112083109</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94189905</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112083107</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2252,6 +2332,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94190080</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2349,6 +2434,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112083108</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2446,8 +2536,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112083126</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>